--- a/test-harness/.tmp/export-dataentry.xlsx
+++ b/test-harness/.tmp/export-dataentry.xlsx
@@ -1253,10 +1253,10 @@
         <v>New on AZT 300mg / 3TC 150mg + NVP 200mg [YX1MQLgAD92]</v>
       </c>
       <c r="GG1" t="str">
-        <v>New on AZT 300mg + 3TC 150mg + ABC 300mg [xETRo03ZfOM]</v>
+        <v>New on AZT 300mg + 3TC 150mg + ABC 300mg  [xETRo03ZfOM]</v>
       </c>
       <c r="GH1" t="str">
-        <v>New on AZT 300mg + 3TC 150mg + TDF 300mg [wIQ5ugpWYUH]</v>
+        <v>New on AZT 300mg + 3TC 150mg + TDF 300mg  [wIQ5ugpWYUH]</v>
       </c>
       <c r="GI1" t="str">
         <v>New on AZT 300mg at 28 wks [GgsWqA0YETj]</v>
@@ -1274,7 +1274,7 @@
         <v>New on d4T 30mg + 3TC 100mg + ABC 300mg [hoj1wTJT6ZW]</v>
       </c>
       <c r="GN1" t="str">
-        <v>New on d4T 30mg + 3TC 100mg + TDF 300mg [SLcj0Swq8rD]</v>
+        <v>New on d4T 30mg + 3TC 100mg + TDF 300mg  [SLcj0Swq8rD]</v>
       </c>
       <c r="GO1" t="str">
         <v>New on d4T 30mg + 3TC 150mg + EFV 600mg [x98jMXibptT]</v>
